--- a/louvers/files/reference_xls/price_xls/cottal_130.xlsx
+++ b/louvers/files/reference_xls/price_xls/cottal_130.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4A1B3B-A0CB-CE49-8F3A-AEE918C29535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F465BC6-2AA5-FB47-A92A-BF4B3B47A151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
   </bookViews>
@@ -1346,38 +1346,31 @@
         <v>61</v>
       </c>
       <c r="B2" s="52">
-        <f>CEILING((C2/10.7639104),10)</f>
-        <v>510</v>
+        <v>561</v>
       </c>
       <c r="C2" s="53">
-        <f>((1000/B6)*'Per m weight'!C35)*A6</f>
-        <v>5444.4444444444443</v>
+        <v>5988.8888888888896</v>
       </c>
       <c r="D2" s="54">
-        <f>+A6*'Per m weight'!C35</f>
-        <v>735</v>
+        <v>808.50000000000011</v>
       </c>
       <c r="E2" s="55">
-        <v>810</v>
+        <v>891.00000000000011</v>
       </c>
       <c r="F2" s="56">
-        <f>C2+(((('Per m weight'!D35/25.4)*39.37)*(1000/B6))*0.25*1.4)</f>
-        <v>6248.1481481481478</v>
+        <v>6872.9629629629635</v>
       </c>
       <c r="G2" s="57">
-        <f>+D2+((('Per m weight'!D35/25.4)*39.3701)*0.25)</f>
-        <v>812.50019685039365</v>
+        <v>893.75021653543308</v>
       </c>
       <c r="H2" s="58">
-        <v>890</v>
+        <v>979.00000000000011</v>
       </c>
       <c r="I2" s="59">
-        <f>C2+(((('Per m weight'!D35/25.4)*39.37)*(1000/B6))*0.45*1.4)</f>
-        <v>6891.1111111111113</v>
+        <v>7580.2222222222226</v>
       </c>
       <c r="J2" s="60">
-        <f>+D2+((('Per m weight'!D35/25.4)*39.3701)*0.6)</f>
-        <v>921.00047244094492</v>
+        <v>1013.1005196850394</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1385,32 +1378,32 @@
         <v>62</v>
       </c>
       <c r="B3" s="42">
-        <f>SUM(B2:B2)</f>
-        <v>510</v>
+        <v>561</v>
       </c>
       <c r="C3" s="43">
-        <f>SUM(C2:C2)</f>
-        <v>5444.4444444444443</v>
-      </c>
-      <c r="D3" s="44"/>
+        <v>5988.8888888888896</v>
+      </c>
+      <c r="D3" s="44">
+        <v>808.50000000000011</v>
+      </c>
       <c r="E3" s="49">
-        <f>SUM(E2:E2)</f>
-        <v>810</v>
+        <v>891.00000000000011</v>
       </c>
       <c r="F3" s="45">
-        <f>SUM(F2:F2)</f>
-        <v>6248.1481481481478</v>
-      </c>
-      <c r="G3" s="50"/>
+        <v>6872.9629629629635</v>
+      </c>
+      <c r="G3" s="50">
+        <v>893.75021653543308</v>
+      </c>
       <c r="H3" s="46">
-        <f>SUM(H2:H2)</f>
-        <v>890</v>
+        <v>979.00000000000011</v>
       </c>
       <c r="I3" s="47">
-        <f>SUM(I2:I2)</f>
-        <v>6891.1111111111113</v>
-      </c>
-      <c r="J3" s="48"/>
+        <v>7580.2222222222226</v>
+      </c>
+      <c r="J3" s="48">
+        <v>1013.1005196850394</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
